--- a/data/trans_bre/P16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,04</t>
+          <t>-3,78; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; -2,79</t>
+          <t>-7,9; -2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,61</t>
+          <t>-3,98; 2,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,41</t>
+          <t>-4,28; -0,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 90,94</t>
+          <t>-66,74; 80,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -50,78</t>
+          <t>-100,0; -53,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 64,66</t>
+          <t>-55,86; 76,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,46; -7,04</t>
+          <t>-71,15; -9,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,44</t>
+          <t>-4,17; 0,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -0,74</t>
+          <t>-5,45; -0,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -0,31</t>
+          <t>-5,88; -0,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -1,3</t>
+          <t>-4,99; -1,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,48; 33,66</t>
+          <t>-85,03; 67,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5,63</t>
+          <t>-100,0; 10,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,39; 9,26</t>
+          <t>-89,82; -2,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,96; -32,19</t>
+          <t>-82,0; -29,98</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 1,4</t>
+          <t>-5,99; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,13</t>
+          <t>-5,13; 1,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,57</t>
+          <t>-5,71; 3,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,98</t>
+          <t>-1,95; 9,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 33,11</t>
+          <t>-81,24; 29,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 28,51</t>
+          <t>-73,69; 28,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 67,59</t>
+          <t>-70,37; 61,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 441,52</t>
+          <t>-27,81; 443,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,07</t>
+          <t>-5,11; -1,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -1,14</t>
+          <t>-4,98; -1,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -1,48</t>
+          <t>-5,52; -1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -2,4</t>
+          <t>-6,59; -2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,99; -15,78</t>
+          <t>-63,1; -17,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,4; -24,09</t>
+          <t>-72,09; -20,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,22; -20,01</t>
+          <t>-68,43; -22,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,22; -38,84</t>
+          <t>-79,83; -38,47</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,08</t>
+          <t>-2,36; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,15</t>
+          <t>-0,82; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,39</t>
+          <t>-3,7; 1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,82</t>
+          <t>-2,06; 2,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 109,97</t>
+          <t>-32,61; 108,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 122,83</t>
+          <t>-11,64; 118,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 26,38</t>
+          <t>-45,16; 28,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 57,74</t>
+          <t>-26,52; 66,14</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,4</t>
+          <t>5,39; 8,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,36</t>
+          <t>1,13; 6,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,99</t>
+          <t>6,41; 10,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,89</t>
+          <t>6,75; 9,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 973,29</t>
+          <t>7,82; 1283,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>518,43; —</t>
+          <t>471,87; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,94</t>
+          <t>-1,21; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,55</t>
+          <t>-1,64; 0,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,62</t>
+          <t>-1,8; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,06</t>
+          <t>-1,55; 1,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 18,71</t>
+          <t>-20,99; 21,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 11,02</t>
+          <t>-27,2; 11,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 11,56</t>
+          <t>-27,81; 10,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 23,26</t>
+          <t>-26,88; 22,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-48,0%</t>
+          <t>-50,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,53</t>
+          <t>-3,45; 2,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -2,52</t>
+          <t>-7,7; -2,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,65</t>
+          <t>-4,2; 2,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,51</t>
+          <t>-4,71; -0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 80,61</t>
+          <t>-59,38; 92,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -53,82</t>
+          <t>-100,0; -59,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 76,89</t>
+          <t>-57,73; 70,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-71,15; -9,83</t>
+          <t>-71,83; -12,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-64,14%</t>
+          <t>-66,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,93</t>
+          <t>-4,38; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,81</t>
+          <t>-5,6; -0,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; -0,39</t>
+          <t>-5,7; -0,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,2</t>
+          <t>-5,21; -1,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 67,08</t>
+          <t>-84,59; 38,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,36</t>
+          <t>-100,0; 1,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,82; -2,31</t>
+          <t>-89,2; 0,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,0; -29,98</t>
+          <t>-83,87; -35,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>-3,23%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,32</t>
+          <t>-5,34; 1,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,21</t>
+          <t>-5,32; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,64</t>
+          <t>-5,64; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,65</t>
+          <t>-3,66; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,24; 29,23</t>
+          <t>-77,8; 35,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 28,75</t>
+          <t>-74,22; 32,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 61,72</t>
+          <t>-72,04; 57,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 443,63</t>
+          <t>-45,36; 94,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,22</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-59,26%</t>
+          <t>-48,55%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -1,1</t>
+          <t>-5,22; -1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -1,11</t>
+          <t>-4,65; -1,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; -1,47</t>
+          <t>-5,41; -1,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -2,32</t>
+          <t>-5,05; -1,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,1; -17,26</t>
+          <t>-63,18; -16,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,09; -20,05</t>
+          <t>-70,73; -21,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,43; -22,64</t>
+          <t>-66,47; -21,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,83; -38,47</t>
+          <t>-62,52; -27,56</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,02</t>
+          <t>-2,29; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,16</t>
+          <t>-0,86; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,45</t>
+          <t>-3,78; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,97</t>
+          <t>0,08; 4,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 108,98</t>
+          <t>-33,19; 105,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 118,3</t>
+          <t>-11,28; 112,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 28,44</t>
+          <t>-46,93; 26,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-26,52; 66,14</t>
+          <t>0,94; 104,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1960,91%</t>
+          <t>1887,46%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,5</t>
+          <t>5,26; 8,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,34</t>
+          <t>1,15; 6,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,09</t>
+          <t>6,27; 9,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,97</t>
+          <t>6,45; 9,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 1283,9</t>
+          <t>10,44; 888,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>471,87; —</t>
+          <t>495,6; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,97%</t>
+          <t>-4,19%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,04</t>
+          <t>-1,28; 0,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,53</t>
+          <t>-1,61; 0,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,55</t>
+          <t>-1,67; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,03</t>
+          <t>-1,17; 0,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 21,1</t>
+          <t>-20,96; 20,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 11,24</t>
+          <t>-27,19; 9,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 10,7</t>
+          <t>-25,55; 11,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 22,57</t>
+          <t>-18,51; 13,56</t>
         </is>
       </c>
     </row>
